--- a/demo_quiz/demo_results.xlsx
+++ b/demo_quiz/demo_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1867,6 +1867,240 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>hh</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>hh</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>60</v>
+      </c>
+      <c r="H38" t="n">
+        <v>6</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>aa</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>aa</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (Prompt Engineering, Machine Learning, Deep Learning, Generative AI)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>20</v>
+      </c>
+      <c r="H39" t="n">
+        <v>8</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:38:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ff</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>fff</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (Prompt Engineering, Machine Learning, Deep Learning, Generative AI)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>40</v>
+      </c>
+      <c r="H40" t="n">
+        <v>11</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:43:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ggg</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>gggg</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (Prompt Engineering, Machine Learning, Deep Learning, Generative AI)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>20</v>
+      </c>
+      <c r="H41" t="n">
+        <v>78</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:46:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>fgvsd</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>efseaf324234</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (Prompt Engineering, Machine Learning, Deep Learning, Generative AI)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>20</v>
+      </c>
+      <c r="H42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:49:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>sgsdg</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>dsgsdg</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (Prompt Engineering, Machine Learning, Deep Learning, Generative AI)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>20</v>
+      </c>
+      <c r="H43" t="n">
+        <v>7</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:52:20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/demo_quiz/demo_results.xlsx
+++ b/demo_quiz/demo_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2101,6 +2101,45 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>hhh</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>lkfnsdflnwe3</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (Prompt Engineering, Machine Learning, Deep Learning, Generative AI)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>40</v>
+      </c>
+      <c r="H44" t="n">
+        <v>11</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-09-11 12:25:10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
